--- a/isolated_excel/Serial Correlation Diagnostics.xlsx
+++ b/isolated_excel/Serial Correlation Diagnostics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Diagnostics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diagnostics'!$A$1:$E$4</definedName>

--- a/isolated_excel/Serial Correlation Diagnostics.xlsx
+++ b/isolated_excel/Serial Correlation Diagnostics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Diagnostics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diagnostics'!$A$1:$E$4</definedName>
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3470172364434945</v>
+        <v>0.3520359755657159</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.000185547850893166</v>
+        <v>0.000139934911654884</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>7.559406236993584e-05</v>
+        <v>6.230754539099949e-05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0001458329375608759</v>
+        <v>7.123636759103555e-05</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1380651276989634</v>
+        <v>-0.1416351891195366</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.13696764466289</v>
+        <v>0.1254749098985961</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.5006736962768379</v>
+        <v>0.4456255431559045</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.3521077833512497</v>
+        <v>0.3138843342034664</v>
       </c>
     </row>
     <row r="4">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.01301373953790651</v>
+        <v>0.01316612202744002</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8885190013988011</v>
+        <v>0.8867407299564685</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.9880414469195714</v>
+        <v>0.9769962252070046</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.8567336779209422</v>
+        <v>0.8757247539116003</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +582,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to May 2026; 113 monthly observations</t>
+          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Serial Correlation Diagnostics.xlsx
+++ b/isolated_excel/Serial Correlation Diagnostics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Diagnostics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diagnostics'!$A$1:$E$4</definedName>
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3520359755657159</v>
+        <v>0.3518264189608741</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.000139934911654884</v>
+        <v>0.0001322452612779051</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6.230754539099949e-05</v>
+        <v>5.670595079073566e-05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7.123636759103555e-05</v>
+        <v>6.444721769888924e-05</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1416351891195366</v>
+        <v>-0.140188581203098</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.1254749098985961</v>
+        <v>0.1277568081678594</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.4456255431559045</v>
+        <v>0.4457248592970166</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.3138843342034664</v>
+        <v>0.3066839911331238</v>
       </c>
     </row>
     <row r="4">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.01316612202744002</v>
+        <v>0.01465478878200355</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8867407299564685</v>
+        <v>0.8735038164340262</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.9769962252070046</v>
+        <v>0.9787208520808428</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.8757247539116003</v>
+        <v>0.8799447076786946</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +582,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
+          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Serial Correlation Diagnostics.xlsx
+++ b/isolated_excel/Serial Correlation Diagnostics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Diagnostics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diagnostics'!$A$1:$E$4</definedName>
@@ -443,7 +443,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3518264189608741</v>
+        <v>0.3518264189608743</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.0001322452612779051</v>
+        <v>0.0001322452612779038</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5.670595079073566e-05</v>
+        <v>5.670595079073489e-05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6.444721769888924e-05</v>
+        <v>6.444721769888872e-05</v>
       </c>
     </row>
     <row r="3">
@@ -503,13 +503,13 @@
         <v>-0.140188581203098</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.1277568081678594</v>
+        <v>0.1277568081678591</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.4457248592970166</v>
+        <v>0.4457248592970162</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.3066839911331238</v>
+        <v>0.3066839911331234</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
         <v>0.8735038164340262</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.9787208520808428</v>
+        <v>0.9787208520808429</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0.8799447076786946</v>
